--- a/stories/arbres/ATOM-SAN.SOM.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir arrive. Brice pousse encore ses petites voitures. Ses yeux piquent. Papa dit : le corps a besoin de dormir. Brice range une voiture. Papa prend le pyjama bleu. Le tissu est doux. Brice met le pyjama. Il glisse un bras, puis l'autre. Ils s'assoient sur le lit. Papa lit une courte histoire. Brice sent son corps se calmer. Parce qu'il a mis le pyjama. Parce que c'est l'heure. Papa baisse la lumière. Brice se couche. C'est le dodo. Papa dit : le dodo aide le corps. Brice ferme les yeux. Le soir, pyjama, puis dodo.</t>
+          <t>Le soir arrive. Brice pousse encore ses petites voitures. Ses yeux piquent. Le corps a besoin de dormir. Brice range une voiture. Papa prend le pyjama bleu. Le tissu est doux. Brice met le pyjama. Il glisse un bras, puis l'autre. Ils s'assoient sur le lit. Papa lit une courte histoire. Brice sent son corps se calmer. Parce qu'il a mis le pyjama. Parce que c'est l'heure. Papa baisse la lumière. Brice se couche. C'est le dodo. Le dodo aide le corps. Brice ferme les yeux. Le soir, pyjama, puis dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir arrive. Brice pousse encore ses petites voitures. Ses yeux piquent.
+papa|Le corps a besoin de dormir.
+narrateur|Brice range une voiture. Papa prend le pyjama bleu. Le tissu est doux. Brice met le pyjama. Il glisse un bras, puis l'autre. Ils s'assoient sur le lit. Papa lit une courte histoire. Brice sent son corps se calmer. Parce qu'il a mis le pyjama. Parce que c'est l'heure. Papa baisse la lumière. Brice se couche. C'est le dodo.
+papa|Le dodo aide le corps.
+narrateur|Brice ferme les yeux. Le soir, pyjama, puis dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, que met Brice avant le dodo ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Brice a mis le pyjama. Il s'est couché. Le soir, le dodo aide le corps.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa pose le livre. Brice respire.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Brice ferme les yeux. Le soir, pyjama, puis dodo.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc,voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Le soir, que met Brice avant le dodo ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,7 @@
           <t>narrateur|Brice a mis le pyjama. Il s'est couché. Le soir, le dodo aide le corps.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1851,7 @@
           <t>narrateur|Papa pose le livre. Brice respire.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.SOM.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brice met le pyjama</t>
+          <t>La voiture rouge sous le canapé</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une voiture rouge brille sous le canapé. Raphaël la range. Papa tend le pyjama bleu. Histoire courte. Raphaël se couche. Soir, pyjama, dodo.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir arrive. Brice pousse encore ses petites voitures. Ses yeux piquent. Le corps a besoin de dormir. Brice range une voiture. Papa prend le pyjama bleu. Le tissu est doux. Brice met le pyjama. Il glisse un bras, puis l'autre. Ils s'assoient sur le lit. Papa lit une courte histoire. Brice sent son corps se calmer. Parce qu'il a mis le pyjama. Parce que c'est l'heure. Papa baisse la lumière. Brice se couche. C'est le dodo. Le dodo aide le corps. Brice ferme les yeux. Le soir, pyjama, puis dodo.</t>
+          <t>Sous le canapé, une petite voiture rouge brille. Le salon sent encore le goûter. Derrière le rideau, le lampadaire fait un carré jaune. Le tapis a un poil tout doux. Une miette dort près de la table. Raphaël vit ici, avec papa et maman. Maman range la cuisine, tout près. En ce moment, Raphaël pousse encore une voiture. Ses yeux piquent un peu. Tes yeux sont fatigués, Raphaël ? Un peu, papa. Le corps a besoin de dormir. On range une voiture. Puis on met le pyjama. Celle-là, sous le canapé ? Oui. On la glisse au garage. Raphaël pousse la voiture rouge. Elle rejoint les autres, sous le canapé. Bravo. Tu as rangé. Viens. Le pyjama bleu t'attend. Papa prend le pyjama. Le tissu est doux, un peu chaud. Il sent le propre. Glisse un bras, puis l'autre. Raphaël met le pyjama. Les manches tombent bien. Bravo. Tu as mis le pyjama. Le soir, pyjama, puis dodo. Ils vont dans la chambre. Le carré jaune du lampadaire reste au salon. Papa ouvre le lit. Ils s'assoient un moment. Une courte histoire ? Oui. Une voiture lente. Papa lit une histoire courte. La voiture roule vers le garage. Raphaël sent son corps se calmer. Parce que tu as mis le pyjama. Parce que c'est l'heure. Ce n'est pas une punition. C'est le dodo. Le dodo aide le corps. Je me couche ? Oui. Tu te couches. Papa baisse la lumière. Raphaël se couche. Il pose la tête. Bravo, Raphaël. Tu as fait du bon travail. Raphaël ferme les yeux. Le soir, pyjama, puis dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir arrive. Brice pousse encore ses petites voitures. Ses yeux piquent.
+          <t>narrateur|Sous le canapé, une petite voiture rouge brille.
+narrateur|Le salon sent encore le goûter.
+narrateur|Derrière le rideau, le lampadaire fait un carré jaune.
+narrateur|Le tapis a un poil tout doux.
+narrateur|Une miette dort près de la table.
+narrateur|Raphaël vit ici, avec papa et maman.
+narrateur|Maman range la cuisine, tout près.
+narrateur|En ce moment, Raphaël pousse encore une voiture.
+narrateur|Ses yeux piquent un peu.
+papa|Tes yeux sont fatigués, Raphaël ?
+enfant-m|Un peu, papa.
 papa|Le corps a besoin de dormir.
-narrateur|Brice range une voiture. Papa prend le pyjama bleu. Le tissu est doux. Brice met le pyjama. Il glisse un bras, puis l'autre. Ils s'assoient sur le lit. Papa lit une courte histoire. Brice sent son corps se calmer. Parce qu'il a mis le pyjama. Parce que c'est l'heure. Papa baisse la lumière. Brice se couche. C'est le dodo.
-papa|Le dodo aide le corps.
-narrateur|Brice ferme les yeux. Le soir, pyjama, puis dodo.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc,voiture_passe</t>
-        </is>
-      </c>
+papa|On range une voiture.
+papa|Puis on met le pyjama.
+enfant-m|Celle-là, sous le canapé ?
+papa|Oui. On la glisse au garage.
+narrateur|Raphaël pousse la voiture rouge.
+narrateur|Elle rejoint les autres, sous le canapé.
+papa|Bravo. Tu as rangé.
+papa|Viens. Le pyjama bleu t'attend.
+narrateur|Papa prend le pyjama.
+narrateur|Le tissu est doux, un peu chaud.
+enfant-m|Il sent le propre.
+papa|Glisse un bras, puis l'autre.
+narrateur|Raphaël met le pyjama.
+narrateur|Les manches tombent bien.
+papa|Bravo. Tu as mis le pyjama.
+papa|Le soir, pyjama, puis dodo.
+narrateur|Ils vont dans la chambre.
+narrateur|Le carré jaune du lampadaire reste au salon.
+narrateur|Papa ouvre le lit.
+narrateur|Ils s'assoient un moment.
+papa|Une courte histoire ?
+enfant-m|Oui. Une voiture lente.
+narrateur|Papa lit une histoire courte.
+narrateur|La voiture roule vers le garage.
+narrateur|Raphaël sent son corps se calmer.
+papa|Parce que tu as mis le pyjama.
+papa|Parce que c'est l'heure.
+papa|Ce n'est pas une punition.
+papa|C'est le dodo. Le dodo aide le corps.
+enfant-m|Je me couche ?
+papa|Oui. Tu te couches.
+narrateur|Papa baisse la lumière.
+narrateur|Raphaël se couche.
+narrateur|Il pose la tête.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Raphaël ferme les yeux.
+narrateur|Le soir, pyjama, puis dodo.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le soir, que met Brice avant le dodo ?</t>
+          <t>Le soir, que met Raphaël avant le dodo ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1561,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, que met Brice avant le dodo ?</t>
+          <t>narrateur|Le soir, que met Raphaël avant le dodo ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Brice a mis le pyjama. Il s'est couché. Le soir, le dodo aide le corps.</t>
+          <t>Raphaël a mis le pyjama. Il s'est couché. Tu as mis le pyjama bleu ? Oui, papa. Bravo. Le soir, le dodo aide le corps. La voiture rouge dort sous le canapé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1733,12 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Brice a mis le pyjama. Il s'est couché. Le soir, le dodo aide le corps.</t>
+          <t>narrateur|Raphaël a mis le pyjama.
+narrateur|Il s'est couché.
+papa|Tu as mis le pyjama bleu ?
+enfant-m|Oui, papa.
+papa|Bravo. Le soir, le dodo aide le corps.
+narrateur|La voiture rouge dort sous le canapé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa pose le livre. Brice respire.</t>
+          <t>Je pose le livre. La voiture est au garage. Oui. Elle attend demain. Raphaël respire. Le pyjama est chaud. Tu es bien couché ? Oui. Le carré jaune s'est éteint un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1848,7 +1906,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa pose le livre. Brice respire.</t>
+          <t>papa|Je pose le livre.
+enfant-m|La voiture est au garage.
+papa|Oui. Elle attend demain.
+narrateur|Raphaël respire.
+narrateur|Le pyjama est chaud.
+papa|Tu es bien couché ?
+enfant-m|Oui.
+narrateur|Le carré jaune s'est éteint un peu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1876,7 +1941,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Puis le dodo. Bravo, Raphaël. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2016,7 +2081,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai mis le pyjama.
+enfant-m|Puis le dodo.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2038,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sous le canapé, une petite voiture rouge brille. Le salon sent encore le goûter. Derrière le rideau, le lampadaire fait un carré jaune. Le tapis a un poil tout doux. Une miette dort près de la table. Raphaël vit ici, avec papa et maman. Maman range la cuisine, tout près. En ce moment, Raphaël pousse encore une voiture. Ses yeux piquent un peu. Tes yeux sont fatigués, Raphaël ? Un peu, papa. Le corps a besoin de dormir. On range une voiture. Puis on met le pyjama. Celle-là, sous le canapé ? Oui. On la glisse au garage. Raphaël pousse la voiture rouge. Elle rejoint les autres, sous le canapé. Bravo. Tu as rangé. Viens. Le pyjama bleu t'attend. Papa prend le pyjama. Le tissu est doux, un peu chaud. Il sent le propre. Glisse un bras, puis l'autre. Raphaël met le pyjama. Les manches tombent bien. Bravo. Tu as mis le pyjama. Le soir, pyjama, puis dodo. Ils vont dans la chambre. Le carré jaune du lampadaire reste au salon. Papa ouvre le lit. Ils s'assoient un moment. Une courte histoire ? Oui. Une voiture lente. Papa lit une histoire courte. La voiture roule vers le garage. Raphaël sent son corps se calmer. Parce que tu as mis le pyjama. Parce que c'est l'heure. Ce n'est pas une punition. C'est le dodo. Le dodo aide le corps. Je me couche ? Oui. Tu te couches. Papa baisse la lumière. Raphaël se couche. Il pose la tête. Bravo, Raphaël. Tu as fait du bon travail. Raphaël ferme les yeux. Le soir, pyjama, puis dodo.</t>
+          <t>Sous le canapé, une petite voiture rouge brille. Une roue est encore tournée vers la porte. Le salon sent encore le goûter. Ça sent le pain, un peu sucré. Derrière le rideau, le lampadaire fait un carré jaune. Le tapis a un poil tout doux. Une miette dort près de la table. Raphaël vit ici, avec papa. La lumière de la cuisine est encore allumée. En ce moment, Raphaël pousse encore une voiture. Ses yeux piquent un peu. Tes yeux sont fatigués, Raphaël ? Un peu, papa. Le corps a besoin de dormir. On range une voiture. Puis on met le pyjama. Celle-là, sous le canapé ? Oui. On la glisse au garage. Raphaël pousse la voiture rouge. Elle rejoint les autres, sous le canapé. Bravo. Tu as rangé. Viens. Le pyjama bleu t'attend. Papa prend le pyjama. Le tissu est doux, un peu chaud. Il sent le propre. Glisse un bras, puis l'autre. Raphaël met le pyjama. Les manches tombent bien. Bravo. Tu as mis le pyjama. Le soir, pyjama, puis dodo. Ils vont dans la chambre. Le carré jaune du lampadaire reste au salon. Papa ouvre le lit. Ils s'assoient un moment. Une courte histoire ? Oui. Une voiture lente. Papa lit une histoire courte. La voiture roule vers le garage. Raphaël sent son corps se calmer. Parce que tu as mis le pyjama. Parce que c'est l'heure. Ce n'est pas une punition. C'est le dodo. Le dodo aide le corps. Je me couche ? Oui. Tu te couches. Papa baisse la lumière. Raphaël se couche. Il pose la tête. Bravo, Raphaël. Raphaël ferme les yeux. Le soir, pyjama, puis dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt; arrive. Brice pousse encore ses petites voitures. Ses yeux piquent. Papa dit : le corps a besoin de dormir. Brice range une voiture. Papa prend le pyjama bleu. Le tissu est doux. Brice met le pyjama. Il glisse un bras, puis l'autre. Ils s'assoient sur le lit. Papa lit une courte histoire. Brice sent son corps se calmer. Parce qu'il a mis le pyjama. Parce que c'est l'heure. Papa baisse la lumière. Brice se couche. C'est le dodo. Papa dit : le dodo aide le corps. Brice ferme les yeux. Le soir, pyjama, puis dodo.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sous le canapé, une petite voiture rouge brille. Une roue est encore tournée vers la porte. Le salon sent encore le goûter. Ça sent le pain, un peu sucré. Derrière le rideau, le lampadaire fait un carré jaune. Le tapis a un poil tout doux. Une miette dort près de la table. Raphaël vit ici, avec papa. La lumière de la cuisine est encore allumée. En ce moment, Raphaël pousse encore une voiture. Ses yeux piquent un peu. Tes yeux sont fatigués, Raphaël ? Un peu, papa. Le corps a besoin de dormir. On range une voiture. Puis on met le pyjama. Celle-là, sous le canapé ? Oui. On la glisse au garage. Raphaël pousse la voiture rouge. Elle rejoint les autres, sous le canapé. Bravo. Tu as rangé. Viens. Le pyjama bleu t'attend. Papa prend le pyjama. Le tissu est doux, un peu chaud. Il sent le propre. Glisse un bras, puis l'autre. Raphaël met le pyjama. Les manches tombent bien. Bravo. Tu as mis le pyjama. Le soir, pyjama, puis dodo. Ils vont dans la chambre. Le carré jaune du lampadaire reste au salon. Papa ouvre le lit. Ils s'assoient un moment. Une courte histoire ? Oui. Une voiture lente. Papa lit une histoire courte. La voiture roule vers le garage. Raphaël sent son corps se calmer. Parce que tu as mis le pyjama. Parce que c'est l'heure. Ce n'est pas une punition. C'est le dodo. Le dodo aide le corps. Je me couche ? Oui. Tu te couches. Papa baisse la lumière. Raphaël se couche. Il pose la tête. Bravo, Raphaël. Raphaël ferme les yeux. Le soir, pyjama, puis dodo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1325,12 +1325,14 @@
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|Sous le canapé, une petite voiture rouge brille.
+narrateur|Une roue est encore tournée vers la porte.
 narrateur|Le salon sent encore le goûter.
+narrateur|Ça sent le pain, un peu sucré.
 narrateur|Derrière le rideau, le lampadaire fait un carré jaune.
 narrateur|Le tapis a un poil tout doux.
 narrateur|Une miette dort près de la table.
-narrateur|Raphaël vit ici, avec papa et maman.
-narrateur|Maman range la cuisine, tout près.
+narrateur|Raphaël vit ici, avec papa.
+narrateur|La lumière de la cuisine est encore allumée.
 narrateur|En ce moment, Raphaël pousse encore une voiture.
 narrateur|Ses yeux piquent un peu.
 papa|Tes yeux sont fatigués, Raphaël ?
@@ -1364,19 +1366,18 @@
 papa|Parce que tu as mis le pyjama.
 papa|Parce que c'est l'heure.
 papa|Ce n'est pas une punition.
-papa|C'est le dodo. Le dodo aide le corps.
+papa|C'est le dodo.
+papa|Le dodo aide le corps.
 enfant-m|Je me couche ?
 papa|Oui. Tu te couches.
 narrateur|Papa baisse la lumière.
 narrateur|Raphaël se couche.
 narrateur|Il pose la tête.
 papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
 narrateur|Raphaël ferme les yeux.
 narrateur|Le soir, pyjama, puis dodo.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1406,7 +1407,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, que met Brice avant le dodo ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le soir, que met Raphaël avant le dodo ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1564,7 +1565,6 @@
           <t>narrateur|Le soir, que met Raphaël avant le dodo ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Brice a mis le pyjama. Il s'est couché. Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, le dodo aide le corps.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a mis le pyjama. Il s'est couché. Tu as mis le pyjama bleu ? Oui, papa. Bravo. Le soir, le dodo aide le corps. La voiture rouge dort sous le canapé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1741,7 +1741,6 @@
 narrateur|La voiture rouge dort sous le canapé.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1771,7 +1770,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa po&lt;emphasis level="moderate"&gt;se&lt;/emphasis&gt; le livre. Brice respire.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pose le livre. La voiture est au garage. Oui. Elle attend demain. Raphaël respire. Le pyjama est chaud. Tu es bien couché ? Oui. Le carré jaune s'est éteint un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1916,7 +1915,6 @@
 narrateur|Le carré jaune s'est éteint un peu.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1941,12 +1939,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai mis le pyjama. Puis le dodo. Bravo, Raphaël. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Puis le dodo. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai mis le pyjama. Puis le dodo. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2083,12 +2081,9 @@
         <is>
           <t>enfant-m|J'ai mis le pyjama.
 enfant-m|Puis le dodo.
-papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Raphaël.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2107,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2152,6 +2147,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brice, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
